--- a/2025/BRIN 3219/Diciembre/BRIN3219-EXPENSAS-Diciembre.xlsx
+++ b/2025/BRIN 3219/Diciembre/BRIN3219-EXPENSAS-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2025\BRIN 3219\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8E4374-9B38-4A34-A525-2B3128563624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B6029C-B13C-47B5-9242-432A25ED25B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -1651,12 +1651,115 @@
     <xf numFmtId="44" fontId="30" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1675,108 +1778,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1801,7 +1802,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2249,16 +2249,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K108"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2273,23 +2273,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217"/>
-      <c r="F2" s="217"/>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="191"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="226">
+      <c r="E3" s="204">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="226"/>
-      <c r="G3" s="226"/>
-      <c r="H3" s="227"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="205"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2325,7 +2325,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2368,14 +2368,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="224"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="225"/>
+      <c r="A12" s="201"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="202"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="203"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2387,17 +2387,17 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="198" t="s">
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="210" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="198"/>
-      <c r="C14" s="198"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="198"/>
-      <c r="F14" s="198"/>
-      <c r="G14" s="198"/>
-      <c r="H14" s="198"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="176" t="s">
@@ -2505,16 +2505,16 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A22" s="220" t="s">
+      <c r="A22" s="197" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="220"/>
-      <c r="C22" s="220"/>
-      <c r="D22" s="220"/>
-      <c r="E22" s="220"/>
-      <c r="F22" s="220"/>
-      <c r="G22" s="220"/>
-      <c r="H22" s="220"/>
+      <c r="B22" s="197"/>
+      <c r="C22" s="197"/>
+      <c r="D22" s="197"/>
+      <c r="E22" s="197"/>
+      <c r="F22" s="197"/>
+      <c r="G22" s="197"/>
+      <c r="H22" s="197"/>
     </row>
     <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="176" t="s">
@@ -2556,16 +2556,16 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="219" t="s">
+      <c r="A26" s="196" t="s">
         <v>130</v>
       </c>
-      <c r="B26" s="219"/>
-      <c r="C26" s="219"/>
-      <c r="D26" s="219"/>
-      <c r="E26" s="219"/>
-      <c r="F26" s="219"/>
-      <c r="G26" s="219"/>
-      <c r="H26" s="219"/>
+      <c r="B26" s="196"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="196"/>
+      <c r="E26" s="196"/>
+      <c r="F26" s="196"/>
+      <c r="G26" s="196"/>
+      <c r="H26" s="196"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="139" t="s">
@@ -2607,16 +2607,16 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="199" t="s">
+      <c r="A30" s="192" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="199"/>
-      <c r="C30" s="199"/>
-      <c r="D30" s="199"/>
-      <c r="E30" s="199"/>
-      <c r="F30" s="199"/>
-      <c r="G30" s="199"/>
-      <c r="H30" s="199"/>
+      <c r="B30" s="192"/>
+      <c r="C30" s="192"/>
+      <c r="D30" s="192"/>
+      <c r="E30" s="192"/>
+      <c r="F30" s="192"/>
+      <c r="G30" s="192"/>
+      <c r="H30" s="192"/>
     </row>
     <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="176"/>
@@ -2673,16 +2673,16 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="199" t="s">
+      <c r="A35" s="192" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="199"/>
-      <c r="C35" s="199"/>
-      <c r="D35" s="199"/>
-      <c r="E35" s="199"/>
-      <c r="F35" s="199"/>
-      <c r="G35" s="199"/>
-      <c r="H35" s="199"/>
+      <c r="B35" s="192"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1">
       <c r="A36" s="139" t="s">
@@ -2728,16 +2728,16 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="198" t="s">
+      <c r="A39" s="210" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="198"/>
-      <c r="C39" s="198"/>
-      <c r="D39" s="198"/>
-      <c r="E39" s="198"/>
-      <c r="F39" s="198"/>
-      <c r="G39" s="198"/>
-      <c r="H39" s="198"/>
+      <c r="B39" s="210"/>
+      <c r="C39" s="210"/>
+      <c r="D39" s="210"/>
+      <c r="E39" s="210"/>
+      <c r="F39" s="210"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="210"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="80" t="s">
@@ -2896,16 +2896,16 @@
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="198" t="s">
+      <c r="A51" s="210" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="198"/>
-      <c r="C51" s="198"/>
-      <c r="D51" s="198"/>
-      <c r="E51" s="198"/>
-      <c r="F51" s="198"/>
-      <c r="G51" s="198"/>
-      <c r="H51" s="198"/>
+      <c r="B51" s="210"/>
+      <c r="C51" s="210"/>
+      <c r="D51" s="210"/>
+      <c r="E51" s="210"/>
+      <c r="F51" s="210"/>
+      <c r="G51" s="210"/>
+      <c r="H51" s="210"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="139" t="s">
@@ -2965,16 +2965,16 @@
       <c r="K55" s="7"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="200" t="s">
+      <c r="A56" s="211" t="s">
         <v>134</v>
       </c>
-      <c r="B56" s="201"/>
-      <c r="C56" s="201"/>
-      <c r="D56" s="201"/>
-      <c r="E56" s="201"/>
-      <c r="F56" s="201"/>
-      <c r="G56" s="201"/>
-      <c r="H56" s="202"/>
+      <c r="B56" s="212"/>
+      <c r="C56" s="212"/>
+      <c r="D56" s="212"/>
+      <c r="E56" s="212"/>
+      <c r="F56" s="212"/>
+      <c r="G56" s="212"/>
+      <c r="H56" s="213"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
       <c r="A57" s="80" t="s">
@@ -3007,16 +3007,16 @@
       </c>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="198" t="s">
+      <c r="A59" s="210" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="198"/>
-      <c r="C59" s="198"/>
-      <c r="D59" s="198"/>
-      <c r="E59" s="198"/>
-      <c r="F59" s="198"/>
-      <c r="G59" s="198"/>
-      <c r="H59" s="198"/>
+      <c r="B59" s="210"/>
+      <c r="C59" s="210"/>
+      <c r="D59" s="210"/>
+      <c r="E59" s="210"/>
+      <c r="F59" s="210"/>
+      <c r="G59" s="210"/>
+      <c r="H59" s="210"/>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
       <c r="A60" s="80"/>
@@ -3067,14 +3067,14 @@
       <c r="I63" s="60"/>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="200"/>
-      <c r="B64" s="201"/>
-      <c r="C64" s="201"/>
-      <c r="D64" s="201"/>
-      <c r="E64" s="201"/>
-      <c r="F64" s="201"/>
-      <c r="G64" s="201"/>
-      <c r="H64" s="202"/>
+      <c r="A64" s="211"/>
+      <c r="B64" s="212"/>
+      <c r="C64" s="212"/>
+      <c r="D64" s="212"/>
+      <c r="E64" s="212"/>
+      <c r="F64" s="212"/>
+      <c r="G64" s="212"/>
+      <c r="H64" s="213"/>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A65" s="81"/>
@@ -3114,60 +3114,60 @@
       </c>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A68" s="211" t="s">
+      <c r="A68" s="219" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="212"/>
-      <c r="C68" s="212"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
-      <c r="F68" s="212"/>
-      <c r="G68" s="212"/>
+      <c r="B68" s="220"/>
+      <c r="C68" s="220"/>
+      <c r="D68" s="220"/>
+      <c r="E68" s="220"/>
+      <c r="F68" s="220"/>
+      <c r="G68" s="220"/>
       <c r="H68" s="164">
         <f>H63</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A69" s="214"/>
-      <c r="B69" s="214"/>
-      <c r="C69" s="214"/>
-      <c r="D69" s="214"/>
-      <c r="E69" s="214"/>
-      <c r="F69" s="214"/>
-      <c r="G69" s="214"/>
-      <c r="H69" s="214"/>
+      <c r="A69" s="187"/>
+      <c r="B69" s="187"/>
+      <c r="C69" s="187"/>
+      <c r="D69" s="187"/>
+      <c r="E69" s="187"/>
+      <c r="F69" s="187"/>
+      <c r="G69" s="187"/>
+      <c r="H69" s="187"/>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A70" s="215"/>
-      <c r="B70" s="215"/>
-      <c r="C70" s="215"/>
-      <c r="D70" s="215"/>
-      <c r="E70" s="215"/>
-      <c r="F70" s="215"/>
-      <c r="G70" s="215"/>
-      <c r="H70" s="215"/>
+      <c r="A70" s="188"/>
+      <c r="B70" s="188"/>
+      <c r="C70" s="188"/>
+      <c r="D70" s="188"/>
+      <c r="E70" s="188"/>
+      <c r="F70" s="188"/>
+      <c r="G70" s="188"/>
+      <c r="H70" s="188"/>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="221" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
-      <c r="D71" s="213"/>
-      <c r="E71" s="213"/>
-      <c r="F71" s="213"/>
-      <c r="G71" s="213"/>
+      <c r="B71" s="221"/>
+      <c r="C71" s="221"/>
+      <c r="D71" s="221"/>
+      <c r="E71" s="221"/>
+      <c r="F71" s="221"/>
+      <c r="G71" s="221"/>
       <c r="H71" s="165"/>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A72" s="221"/>
-      <c r="B72" s="222"/>
-      <c r="C72" s="222"/>
-      <c r="D72" s="222"/>
-      <c r="E72" s="222"/>
-      <c r="F72" s="222"/>
-      <c r="G72" s="223"/>
+      <c r="A72" s="198"/>
+      <c r="B72" s="199"/>
+      <c r="C72" s="199"/>
+      <c r="D72" s="199"/>
+      <c r="E72" s="199"/>
+      <c r="F72" s="199"/>
+      <c r="G72" s="200"/>
       <c r="H72" s="73"/>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
@@ -3196,54 +3196,54 @@
       <c r="H74" s="131"/>
     </row>
     <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="194" t="s">
+      <c r="A75" s="206" t="s">
         <v>82</v>
       </c>
-      <c r="B75" s="195"/>
-      <c r="C75" s="195"/>
-      <c r="D75" s="195"/>
-      <c r="E75" s="195"/>
-      <c r="F75" s="195"/>
-      <c r="G75" s="195"/>
+      <c r="B75" s="207"/>
+      <c r="C75" s="207"/>
+      <c r="D75" s="207"/>
+      <c r="E75" s="207"/>
+      <c r="F75" s="207"/>
+      <c r="G75" s="207"/>
       <c r="H75" s="132">
         <f>H73</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A76" s="206" t="s">
+      <c r="A76" s="193" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="207"/>
-      <c r="C76" s="207"/>
-      <c r="D76" s="207"/>
-      <c r="E76" s="207"/>
-      <c r="F76" s="207"/>
-      <c r="G76" s="208"/>
+      <c r="B76" s="194"/>
+      <c r="C76" s="194"/>
+      <c r="D76" s="194"/>
+      <c r="E76" s="194"/>
+      <c r="F76" s="194"/>
+      <c r="G76" s="195"/>
       <c r="H76" s="132"/>
     </row>
     <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A77" s="206" t="s">
+      <c r="A77" s="193" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="207"/>
-      <c r="C77" s="207"/>
-      <c r="D77" s="207"/>
-      <c r="E77" s="207"/>
-      <c r="F77" s="207"/>
-      <c r="G77" s="208"/>
+      <c r="B77" s="194"/>
+      <c r="C77" s="194"/>
+      <c r="D77" s="194"/>
+      <c r="E77" s="194"/>
+      <c r="F77" s="194"/>
+      <c r="G77" s="195"/>
       <c r="H77" s="132"/>
     </row>
-    <row r="78" spans="1:11" ht="18.75">
-      <c r="A78" s="194" t="s">
+    <row r="78" spans="1:11" ht="18">
+      <c r="A78" s="206" t="s">
         <v>89</v>
       </c>
-      <c r="B78" s="195"/>
-      <c r="C78" s="195"/>
-      <c r="D78" s="195"/>
-      <c r="E78" s="195"/>
-      <c r="F78" s="195"/>
-      <c r="G78" s="195"/>
+      <c r="B78" s="207"/>
+      <c r="C78" s="207"/>
+      <c r="D78" s="207"/>
+      <c r="E78" s="207"/>
+      <c r="F78" s="207"/>
+      <c r="G78" s="207"/>
       <c r="H78" s="132">
         <f>H29+H38+H50+H55+H58+H34+H21+H25</f>
         <v>4494890.1399999997</v>
@@ -3251,34 +3251,34 @@
       <c r="J78" s="173"/>
       <c r="K78" s="144"/>
     </row>
-    <row r="79" spans="1:11" ht="18.75">
-      <c r="A79" s="203" t="s">
+    <row r="79" spans="1:11" ht="18">
+      <c r="A79" s="214" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="204"/>
-      <c r="C79" s="204"/>
-      <c r="D79" s="204"/>
-      <c r="E79" s="204"/>
-      <c r="F79" s="204"/>
-      <c r="G79" s="205"/>
+      <c r="B79" s="215"/>
+      <c r="C79" s="215"/>
+      <c r="D79" s="215"/>
+      <c r="E79" s="215"/>
+      <c r="F79" s="215"/>
+      <c r="G79" s="216"/>
       <c r="H79" s="133">
         <f>H76+H78</f>
         <v>4494890.1399999997</v>
       </c>
       <c r="I79" s="128"/>
-      <c r="J79" s="186"/>
-      <c r="K79" s="186"/>
-    </row>
-    <row r="80" spans="1:11" ht="18.75">
-      <c r="A80" s="203" t="s">
+      <c r="J79" s="222"/>
+      <c r="K79" s="222"/>
+    </row>
+    <row r="80" spans="1:11" ht="18">
+      <c r="A80" s="214" t="s">
         <v>94</v>
       </c>
-      <c r="B80" s="204"/>
-      <c r="C80" s="204"/>
-      <c r="D80" s="204"/>
-      <c r="E80" s="204"/>
-      <c r="F80" s="204"/>
-      <c r="G80" s="205"/>
+      <c r="B80" s="215"/>
+      <c r="C80" s="215"/>
+      <c r="D80" s="215"/>
+      <c r="E80" s="215"/>
+      <c r="F80" s="215"/>
+      <c r="G80" s="216"/>
       <c r="H80" s="134">
         <f>H77+H75</f>
         <v>0</v>
@@ -3286,38 +3286,38 @@
       <c r="J80" s="144"/>
     </row>
     <row r="81" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A81" s="209" t="s">
+      <c r="A81" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="210"/>
-      <c r="C81" s="210"/>
-      <c r="D81" s="210"/>
-      <c r="E81" s="210"/>
-      <c r="F81" s="210"/>
-      <c r="G81" s="210"/>
+      <c r="B81" s="218"/>
+      <c r="C81" s="218"/>
+      <c r="D81" s="218"/>
+      <c r="E81" s="218"/>
+      <c r="F81" s="218"/>
+      <c r="G81" s="218"/>
       <c r="H81" s="135">
         <f>H78+H75</f>
         <v>4494890.1399999997</v>
       </c>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:11" ht="18.75" hidden="1">
-      <c r="A82" s="196" t="s">
+    <row r="82" spans="1:11" ht="18" hidden="1">
+      <c r="A82" s="208" t="s">
         <v>17</v>
       </c>
-      <c r="B82" s="197"/>
-      <c r="C82" s="197"/>
-      <c r="D82" s="197"/>
-      <c r="E82" s="197"/>
-      <c r="F82" s="197"/>
-      <c r="G82" s="197"/>
+      <c r="B82" s="209"/>
+      <c r="C82" s="209"/>
+      <c r="D82" s="209"/>
+      <c r="E82" s="209"/>
+      <c r="F82" s="209"/>
+      <c r="G82" s="209"/>
       <c r="H82" s="136">
         <f>H67</f>
         <v>0</v>
       </c>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="18.75" hidden="1">
+    <row r="83" spans="1:11" ht="18" hidden="1">
       <c r="A83" s="137"/>
       <c r="B83" s="137"/>
       <c r="C83" s="137"/>
@@ -3328,7 +3328,7 @@
       <c r="H83" s="138"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:11" ht="18.75" hidden="1">
+    <row r="84" spans="1:11" ht="18" hidden="1">
       <c r="A84" s="137"/>
       <c r="B84" s="137"/>
       <c r="C84" s="137"/>
@@ -3339,7 +3339,7 @@
       <c r="H84" s="138"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:11" ht="18.75" hidden="1">
+    <row r="85" spans="1:11" ht="18" hidden="1">
       <c r="A85" s="137"/>
       <c r="B85" s="137"/>
       <c r="C85" s="137"/>
@@ -3360,19 +3360,19 @@
       <c r="G86" s="139"/>
       <c r="H86" s="139"/>
     </row>
-    <row r="87" spans="1:11" ht="18.75">
-      <c r="A87" s="191" t="s">
+    <row r="87" spans="1:11" ht="18">
+      <c r="A87" s="226" t="s">
         <v>10</v>
       </c>
-      <c r="B87" s="192"/>
-      <c r="C87" s="192"/>
-      <c r="D87" s="192"/>
-      <c r="E87" s="192"/>
-      <c r="F87" s="192"/>
-      <c r="G87" s="192"/>
-      <c r="H87" s="193"/>
-    </row>
-    <row r="88" spans="1:11" ht="18.75">
+      <c r="B87" s="227"/>
+      <c r="C87" s="227"/>
+      <c r="D87" s="227"/>
+      <c r="E87" s="227"/>
+      <c r="F87" s="227"/>
+      <c r="G87" s="227"/>
+      <c r="H87" s="228"/>
+    </row>
+    <row r="88" spans="1:11" ht="18">
       <c r="A88" s="140" t="s">
         <v>12</v>
       </c>
@@ -3476,7 +3476,7 @@
       <c r="G94" s="4"/>
       <c r="H94" s="98"/>
     </row>
-    <row r="95" spans="1:11" ht="18.75">
+    <row r="95" spans="1:11" ht="18">
       <c r="A95" s="22" t="s">
         <v>11</v>
       </c>
@@ -3491,20 +3491,20 @@
         <v>3532612.5527224625</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="97" spans="1:8" ht="16.5" thickBot="1">
-      <c r="A97" s="188" t="s">
+    <row r="96" spans="1:11" ht="15" thickBot="1"/>
+    <row r="97" spans="1:8" ht="16.2" thickBot="1">
+      <c r="A97" s="223" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="189"/>
-      <c r="C97" s="189"/>
-      <c r="D97" s="189"/>
-      <c r="E97" s="189"/>
-      <c r="F97" s="189"/>
-      <c r="G97" s="189"/>
-      <c r="H97" s="190"/>
-    </row>
-    <row r="98" spans="1:8" ht="15.75">
+      <c r="B97" s="224"/>
+      <c r="C97" s="224"/>
+      <c r="D97" s="224"/>
+      <c r="E97" s="224"/>
+      <c r="F97" s="224"/>
+      <c r="G97" s="224"/>
+      <c r="H97" s="225"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.6">
       <c r="A98" s="87" t="s">
         <v>12</v>
       </c>
@@ -3566,56 +3566,51 @@
       </c>
     </row>
     <row r="105" spans="1:8" hidden="1">
-      <c r="A105" s="187"/>
-      <c r="B105" s="187"/>
-      <c r="C105" s="187"/>
-      <c r="D105" s="187"/>
-      <c r="E105" s="187"/>
-      <c r="F105" s="187"/>
-      <c r="G105" s="187"/>
-      <c r="H105" s="187"/>
+      <c r="A105" s="202"/>
+      <c r="B105" s="202"/>
+      <c r="C105" s="202"/>
+      <c r="D105" s="202"/>
+      <c r="E105" s="202"/>
+      <c r="F105" s="202"/>
+      <c r="G105" s="202"/>
+      <c r="H105" s="202"/>
     </row>
     <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="187"/>
-      <c r="B106" s="187"/>
-      <c r="C106" s="187"/>
-      <c r="D106" s="187"/>
-      <c r="E106" s="187"/>
-      <c r="F106" s="187"/>
-      <c r="G106" s="187"/>
-      <c r="H106" s="187"/>
+      <c r="A106" s="202"/>
+      <c r="B106" s="202"/>
+      <c r="C106" s="202"/>
+      <c r="D106" s="202"/>
+      <c r="E106" s="202"/>
+      <c r="F106" s="202"/>
+      <c r="G106" s="202"/>
+      <c r="H106" s="202"/>
     </row>
     <row r="107" spans="1:8" hidden="1">
-      <c r="A107" s="187"/>
-      <c r="B107" s="187"/>
-      <c r="C107" s="187"/>
-      <c r="D107" s="187"/>
-      <c r="E107" s="187"/>
-      <c r="F107" s="187"/>
-      <c r="G107" s="187"/>
-      <c r="H107" s="187"/>
+      <c r="A107" s="202"/>
+      <c r="B107" s="202"/>
+      <c r="C107" s="202"/>
+      <c r="D107" s="202"/>
+      <c r="E107" s="202"/>
+      <c r="F107" s="202"/>
+      <c r="G107" s="202"/>
+      <c r="H107" s="202"/>
     </row>
     <row r="108" spans="1:8" hidden="1">
-      <c r="A108" s="187"/>
-      <c r="B108" s="187"/>
-      <c r="C108" s="187"/>
-      <c r="D108" s="187"/>
-      <c r="E108" s="187"/>
-      <c r="F108" s="187"/>
-      <c r="G108" s="187"/>
-      <c r="H108" s="187"/>
+      <c r="A108" s="202"/>
+      <c r="B108" s="202"/>
+      <c r="C108" s="202"/>
+      <c r="D108" s="202"/>
+      <c r="E108" s="202"/>
+      <c r="F108" s="202"/>
+      <c r="G108" s="202"/>
+      <c r="H108" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A69:H70"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A105:H108"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="A14:H14"/>
@@ -3632,10 +3627,15 @@
     <mergeCell ref="A68:G68"/>
     <mergeCell ref="A75:G75"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="A105:H108"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A69:H70"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="E3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3646,23 +3646,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3751,11 +3751,11 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="229">
+      <c r="B5" s="230">
         <f>C3</f>
         <v>2782455.8899999997</v>
       </c>
-      <c r="C5" s="229"/>
+      <c r="C5" s="230"/>
       <c r="D5" s="21"/>
       <c r="E5" s="121">
         <v>70000</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="231" t="s">
+      <c r="B6" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="232"/>
+      <c r="C6" s="233"/>
       <c r="D6" s="21"/>
       <c r="E6" s="119"/>
       <c r="F6" s="114"/>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="229">
+      <c r="B7" s="230">
         <v>2000000</v>
       </c>
-      <c r="C7" s="229"/>
+      <c r="C7" s="230"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="114"/>
@@ -4843,7 +4843,7 @@
         <f t="shared" si="5"/>
         <v>3046839.1915586414</v>
       </c>
-      <c r="O27" s="236">
+      <c r="O27" s="186">
         <f>L27+M27</f>
         <v>197993.67384599999</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>197993.67384599999</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75">
+    <row r="32" spans="1:17" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5102,114 +5102,119 @@
         <v>15883307.414084934</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
+    <row r="33" spans="1:14" ht="14.25" customHeight="1">
+      <c r="L33" s="7">
+        <f>L29/2</f>
+        <v>53562.275882499991</v>
+      </c>
+    </row>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="228"/>
-      <c r="I34" s="228"/>
-      <c r="J34" s="228"/>
-      <c r="K34" s="228"/>
-      <c r="L34" s="228"/>
-      <c r="M34" s="228"/>
-      <c r="N34" s="228"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
+      <c r="M34" s="229"/>
+      <c r="N34" s="229"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="228"/>
-      <c r="C35" s="228"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="228"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="228"/>
-      <c r="L35" s="228"/>
-      <c r="M35" s="228"/>
-      <c r="N35" s="228"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
+      <c r="K35" s="229"/>
+      <c r="L35" s="229"/>
+      <c r="M35" s="229"/>
+      <c r="N35" s="229"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="228"/>
-      <c r="C36" s="228"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="228"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="228"/>
-      <c r="L36" s="228"/>
-      <c r="M36" s="228"/>
-      <c r="N36" s="228"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="229"/>
+      <c r="J36" s="229"/>
+      <c r="K36" s="229"/>
+      <c r="L36" s="229"/>
+      <c r="M36" s="229"/>
+      <c r="N36" s="229"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="228"/>
-      <c r="C37" s="228"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
-      <c r="G37" s="228"/>
-      <c r="H37" s="228"/>
-      <c r="I37" s="228"/>
-      <c r="J37" s="228"/>
-      <c r="K37" s="228"/>
-      <c r="L37" s="228"/>
-      <c r="M37" s="228"/>
-      <c r="N37" s="228"/>
+      <c r="B37" s="229"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="229"/>
+      <c r="J37" s="229"/>
+      <c r="K37" s="229"/>
+      <c r="L37" s="229"/>
+      <c r="M37" s="229"/>
+      <c r="N37" s="229"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="230"/>
-      <c r="B38" s="230"/>
-      <c r="C38" s="230"/>
-      <c r="D38" s="230"/>
-      <c r="E38" s="230"/>
-      <c r="F38" s="230"/>
-      <c r="G38" s="230"/>
-      <c r="H38" s="230"/>
-      <c r="I38" s="230"/>
-      <c r="J38" s="230"/>
-      <c r="K38" s="230"/>
-      <c r="L38" s="230"/>
-      <c r="M38" s="230"/>
-      <c r="N38" s="230"/>
+      <c r="A38" s="231"/>
+      <c r="B38" s="231"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="231"/>
+      <c r="G38" s="231"/>
+      <c r="H38" s="231"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="231"/>
+      <c r="N38" s="231"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="230"/>
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="230"/>
-      <c r="J39" s="230"/>
-      <c r="K39" s="230"/>
-      <c r="L39" s="230"/>
-      <c r="M39" s="230"/>
-      <c r="N39" s="230"/>
+      <c r="A39" s="231"/>
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="231"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="230"/>
-      <c r="B40" s="230"/>
-      <c r="C40" s="230"/>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="230"/>
-      <c r="N40" s="230"/>
+      <c r="A40" s="231"/>
+      <c r="B40" s="231"/>
+      <c r="C40" s="231"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -5223,7 +5228,7 @@
     <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="7" scale="65" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -5231,25 +5236,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="234" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="235"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5285,13 +5290,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+    <row r="7" spans="1:7" ht="15" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="30.75" thickBot="1">
+    <row r="8" spans="1:7" ht="29.4" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5652,7 +5657,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75">
+    <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5674,7 +5679,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
+    <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5696,7 +5701,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
+    <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5718,7 +5723,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
+    <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5744,7 +5749,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
+    <row r="28" spans="1:7" ht="15.6">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5766,7 +5771,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
+    <row r="29" spans="1:7" ht="15.6">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5788,7 +5793,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.6">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5810,7 +5815,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75">
+    <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5832,7 +5837,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75">
+    <row r="32" spans="1:7" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
